--- a/RST_SniperAI_Features_Automation/src/test/resources/TestDocuments/SAI_Login_Funtionality.xlsx
+++ b/RST_SniperAI_Features_Automation/src/test/resources/TestDocuments/SAI_Login_Funtionality.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B68667CE-ECC9-4AAB-8361-A9265DD0E2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F06CB540-0F0C-4B80-B962-FF8A0615972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,9 +15,9 @@
     <sheet name="ForgetPassword" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <oleSize ref="A1:C3"/>
+  <oleSize ref="C1:F3"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="90">
   <si>
     <t>Sr No</t>
   </si>
@@ -281,12 +281,37 @@
   </si>
   <si>
     <t>TC_007: Passed</t>
+  </si>
+  <si>
+    <t>TC_008: Passed</t>
+  </si>
+  <si>
+    <t>TC_009: Passed</t>
+  </si>
+  <si>
+    <t>TC_010: Passed</t>
+  </si>
+  <si>
+    <t>TC_012: Passed</t>
+  </si>
+  <si>
+    <t>TC_011: Passed</t>
+  </si>
+  <si>
+    <t>TC_013: Passed</t>
+  </si>
+  <si>
+    <t>TC_014: Passed</t>
+  </si>
+  <si>
+    <t>TC_001: Failed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -312,7 +337,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -332,6 +357,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
         <fgColor indexed="10"/>
       </patternFill>
     </fill>
@@ -388,7 +423,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -425,6 +460,55 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -743,13 +827,13 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="6.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="3" width="12.109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="3" width="26.6640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="3" width="10.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="37.6640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="14.0"/>
+    <col min="7" max="16384" style="3" width="9.109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -840,11 +924,11 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="7.109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="66.109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="37.33203125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="13.77734375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -874,7 +958,7 @@
       <c r="C2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="27" t="s">
         <v>73</v>
       </c>
       <c r="E2" s="9"/>
@@ -889,7 +973,7 @@
       <c r="C3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="28" t="s">
         <v>74</v>
       </c>
       <c r="E3" s="9"/>
@@ -904,7 +988,7 @@
       <c r="C4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="29" t="s">
         <v>75</v>
       </c>
       <c r="E4" s="9"/>
@@ -919,8 +1003,8 @@
       <c r="C5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>76</v>
+      <c r="D5" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="E5" s="9"/>
     </row>
@@ -934,7 +1018,7 @@
       <c r="C6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="32" t="s">
         <v>78</v>
       </c>
       <c r="E6" s="9"/>
@@ -949,8 +1033,8 @@
       <c r="C7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>77</v>
+      <c r="D7" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="E7" s="9"/>
     </row>
@@ -982,12 +1066,12 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="7.109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="79.44140625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="59.21875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="13.77734375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.109375"/>
+    <col min="6" max="16384" style="1" width="9.109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1017,8 +1101,8 @@
       <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>73</v>
+      <c r="D2" s="34" t="s">
+        <v>89</v>
       </c>
       <c r="E2" s="2"/>
     </row>
@@ -1032,7 +1116,7 @@
       <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="33" t="s">
         <v>74</v>
       </c>
       <c r="E3" s="2"/>
@@ -1047,7 +1131,7 @@
       <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="35" t="s">
         <v>75</v>
       </c>
       <c r="E4" s="2"/>
@@ -1062,7 +1146,7 @@
       <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="36" t="s">
         <v>79</v>
       </c>
       <c r="E5" s="2"/>
@@ -1077,7 +1161,7 @@
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="37" t="s">
         <v>78</v>
       </c>
       <c r="E6" s="2"/>
@@ -1092,7 +1176,7 @@
       <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="38" t="s">
         <v>80</v>
       </c>
       <c r="E7" s="2"/>
@@ -1107,7 +1191,7 @@
       <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="39" t="s">
         <v>81</v>
       </c>
       <c r="E8" s="2"/>
@@ -1122,7 +1206,9 @@
       <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="40" t="s">
+        <v>82</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
   </sheetData>
@@ -1135,11 +1221,11 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="78.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="7.109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="78.33203125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="59.21875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="13.77734375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1169,7 +1255,7 @@
       <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="42" t="s">
         <v>73</v>
       </c>
       <c r="E2" s="2"/>
@@ -1184,7 +1270,9 @@
       <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="41" t="s">
+        <v>74</v>
+      </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1197,7 +1285,9 @@
       <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="43" t="s">
+        <v>75</v>
+      </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1210,7 +1300,9 @@
       <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="44" t="s">
+        <v>79</v>
+      </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1223,7 +1315,9 @@
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="45" t="s">
+        <v>78</v>
+      </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1236,7 +1330,9 @@
       <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="46" t="s">
+        <v>80</v>
+      </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,7 +1345,9 @@
       <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="47" t="s">
+        <v>81</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1262,7 +1360,9 @@
       <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="48" t="s">
+        <v>82</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
   </sheetData>
@@ -1275,12 +1375,12 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="84.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="37.44140625" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="8"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="8" width="7.109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="8" width="84.6640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="8" width="64.44140625"/>
+    <col min="4" max="4" customWidth="true" style="16" width="14.77734375"/>
+    <col min="5" max="5" customWidth="true" style="8" width="37.44140625"/>
+    <col min="6" max="16384" style="8" width="9.109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1310,7 +1410,9 @@
       <c r="C2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="9"/>
+      <c r="D2" s="49" t="s">
+        <v>73</v>
+      </c>
       <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -1323,7 +1425,7 @@
       <c r="C3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="15"/>
       <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -1336,7 +1438,7 @@
       <c r="C4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="9"/>
+      <c r="D4" s="15"/>
       <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -1349,7 +1451,7 @@
       <c r="C5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="15"/>
       <c r="E5" s="9"/>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1362,7 +1464,9 @@
       <c r="C6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="50" t="s">
+        <v>78</v>
+      </c>
       <c r="E6" s="9"/>
     </row>
     <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -1375,7 +1479,7 @@
       <c r="C7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="15"/>
       <c r="E7" s="9"/>
     </row>
     <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -1388,7 +1492,7 @@
       <c r="C8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="15"/>
       <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -1401,7 +1505,7 @@
       <c r="C9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="15"/>
       <c r="E9" s="9"/>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1414,7 +1518,9 @@
       <c r="C10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="51" t="s">
+        <v>83</v>
+      </c>
       <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1427,7 +1533,9 @@
       <c r="C11" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="52" t="s">
+        <v>84</v>
+      </c>
       <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1440,7 +1548,9 @@
       <c r="C12" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1453,7 +1563,9 @@
       <c r="C13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="54" t="s">
+        <v>85</v>
+      </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1466,7 +1578,9 @@
       <c r="C14" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="55" t="s">
+        <v>87</v>
+      </c>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1479,7 +1593,9 @@
       <c r="C15" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="56" t="s">
+        <v>88</v>
+      </c>
       <c r="E15" s="9"/>
     </row>
   </sheetData>

--- a/RST_SniperAI_Features_Automation/src/test/resources/TestDocuments/SAI_Login_Funtionality.xlsx
+++ b/RST_SniperAI_Features_Automation/src/test/resources/TestDocuments/SAI_Login_Funtionality.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F06CB540-0F0C-4B80-B962-FF8A0615972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83912CF0-E6F1-4A7F-B8C3-53C0C7D38E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Data" sheetId="5" r:id="rId1"/>
@@ -13,9 +13,11 @@
     <sheet name="RecruiterModule_Login" sheetId="1" r:id="rId3"/>
     <sheet name="CandidateModule_Login" sheetId="2" r:id="rId4"/>
     <sheet name="ForgetPassword" sheetId="3" r:id="rId5"/>
+    <sheet name="SignupPage" sheetId="6" r:id="rId6"/>
+    <sheet name="JobOpeningsPage" sheetId="7" r:id="rId7"/>
+    <sheet name="CandidateModule" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <oleSize ref="C1:F3"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="93">
   <si>
     <t>Sr No</t>
   </si>
@@ -256,55 +260,64 @@
     <t>Verify and check select candidate checkbox, click on the forgot password, without adding email and click on reset password button.</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify and check user will be able to add the texts in all the text boxes from sign up page. </t>
+  </si>
+  <si>
+    <t>Verify and check user will not be able to add invalid data inside the text boxes</t>
+  </si>
+  <si>
+    <t>Verify and check all the alerts will be showing proper for all the required fields on the sign up page and user will not be able to create an account with empty mandatory fields.</t>
+  </si>
+  <si>
+    <t>Verify and check user will be able to redirected to terms and conditions page when click on the terms page.</t>
+  </si>
+  <si>
+    <t>Verify and check user will be able to click on already signed up button and once click user will be redirected to the login page.</t>
+  </si>
+  <si>
+    <t>Verify and check the social media icons will be showing proper links and user will be able to click on those links from the sign up page.</t>
+  </si>
+  <si>
+    <t>Verify and check help me option will be clickable on the sign up page</t>
+  </si>
+  <si>
+    <t>Verify and check all the sorting filters will be working proper on the job openings page</t>
+  </si>
+  <si>
+    <t>Verify and check the column filters will be working proper on the job openings page'</t>
+  </si>
+  <si>
+    <t>Verify and check the reset button will be working proper</t>
+  </si>
+  <si>
+    <t>Verify and check once user click on the apply button from job list page then that user redirected to the sign up page.</t>
+  </si>
+  <si>
+    <t>Verify and check user will be able to click on the job title page, once user click on that option then that user will be redirected to the job details page.</t>
+  </si>
+  <si>
+    <t>Verify and check user will be able to click on the apply button from the job details page and once click then that redirected to the sign up page.</t>
+  </si>
+  <si>
+    <t>Verify and check with click on the apply button from the job list page and login the  candidate module.</t>
+  </si>
+  <si>
+    <t>Verify and check with click on the apply button from the job details page and login the  candidate module.</t>
+  </si>
+  <si>
+    <t>Verify and check with click on the back to job openings button from the job details page then user will be redirected to the job openings page.</t>
+  </si>
+  <si>
+    <t>Verify and check with click on the apply button for new job which is not applied by candidate previously.</t>
+  </si>
+  <si>
+    <t>Verify and check with click on the apply button for existing job for which candidate is already applied.</t>
+  </si>
+  <si>
+    <t>Verify and check the pagination will be working fine</t>
+  </si>
+  <si>
     <t>TC_001: Passed</t>
-  </si>
-  <si>
-    <t>TC_002: Passed</t>
-  </si>
-  <si>
-    <t>TC_003: Passed</t>
-  </si>
-  <si>
-    <t>TC_004: Failed</t>
-  </si>
-  <si>
-    <t>TC_006: Failed</t>
-  </si>
-  <si>
-    <t>TC_005: Passed</t>
-  </si>
-  <si>
-    <t>TC_004: Passed</t>
-  </si>
-  <si>
-    <t>TC_006: Passed</t>
-  </si>
-  <si>
-    <t>TC_007: Passed</t>
-  </si>
-  <si>
-    <t>TC_008: Passed</t>
-  </si>
-  <si>
-    <t>TC_009: Passed</t>
-  </si>
-  <si>
-    <t>TC_010: Passed</t>
-  </si>
-  <si>
-    <t>TC_012: Passed</t>
-  </si>
-  <si>
-    <t>TC_011: Passed</t>
-  </si>
-  <si>
-    <t>TC_013: Passed</t>
-  </si>
-  <si>
-    <t>TC_014: Passed</t>
-  </si>
-  <si>
-    <t>TC_001: Failed</t>
   </si>
 </sst>
 </file>
@@ -312,7 +325,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,7 +350,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,23 +364,13 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
+      <patternFill patternType="none">
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
         <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -423,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -458,57 +461,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -825,18 +781,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75AB278-AB38-496E-9671-3EAB0B2FE2B5}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="6.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="3" width="12.109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="3" width="26.6640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="3" width="12.140625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="3" width="26.7109375"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="3" width="10.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="37.6640625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="37.7109375"/>
     <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="14.0"/>
-    <col min="7" max="16384" style="3" width="9.109375"/>
+    <col min="7" max="16384" style="3" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -856,7 +812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -876,7 +832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="10">
         <f>A2+1</f>
         <v>2</v>
@@ -897,7 +853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="10">
         <f>A3+1</f>
         <v>3</v>
@@ -922,16 +878,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38218D55-1662-476D-AD98-52D1E9A44BBC}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="7.109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="66.109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="37.33203125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="13.77734375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.109375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="7.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="71.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="40.42578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="6.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
@@ -948,7 +904,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
@@ -958,12 +914,10 @@
       <c r="C2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>73</v>
-      </c>
+      <c r="D2" s="9"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
@@ -973,12 +927,10 @@
       <c r="C3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="28" t="s">
-        <v>74</v>
-      </c>
+      <c r="D3" s="9"/>
       <c r="E3" s="9"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="9" t="s">
         <v>23</v>
       </c>
@@ -988,12 +940,10 @@
       <c r="C4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>75</v>
-      </c>
+      <c r="D4" s="9"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
@@ -1003,12 +953,10 @@
       <c r="C5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
@@ -1018,12 +966,10 @@
       <c r="C6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="32" t="s">
-        <v>78</v>
-      </c>
+      <c r="D6" s="9"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="9" t="s">
         <v>32</v>
       </c>
@@ -1033,12 +979,10 @@
       <c r="C7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>80</v>
-      </c>
+      <c r="D7" s="9"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="9" t="s">
         <v>35</v>
       </c>
@@ -1047,7 +991,7 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="9" t="s">
         <v>36</v>
       </c>
@@ -1064,17 +1008,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="7.109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="79.44140625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="59.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="13.77734375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.109375"/>
-    <col min="6" max="16384" style="1" width="9.109375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="7.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="86.5703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="64.42578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="6.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="6" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="3" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
@@ -1091,7 +1035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30.75">
       <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
@@ -1101,12 +1045,10 @@
       <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="34" t="s">
-        <v>89</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="30.75">
       <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
@@ -1116,12 +1058,10 @@
       <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="33" t="s">
-        <v>74</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="30.75">
       <c r="A4" s="9" t="s">
         <v>23</v>
       </c>
@@ -1131,12 +1071,10 @@
       <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="35" t="s">
-        <v>75</v>
-      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30.75">
       <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
@@ -1146,12 +1084,10 @@
       <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>79</v>
-      </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="30.75">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
@@ -1161,12 +1097,10 @@
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="37" t="s">
-        <v>78</v>
-      </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="30.75">
       <c r="A7" s="9" t="s">
         <v>32</v>
       </c>
@@ -1176,12 +1110,10 @@
       <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="38" t="s">
-        <v>80</v>
-      </c>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="30.75">
       <c r="A8" s="9" t="s">
         <v>35</v>
       </c>
@@ -1191,12 +1123,10 @@
       <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>81</v>
-      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="30.75">
       <c r="A9" s="9" t="s">
         <v>36</v>
       </c>
@@ -1206,9 +1136,7 @@
       <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="40" t="s">
-        <v>82</v>
-      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
   </sheetData>
@@ -1219,16 +1147,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8811CEF-6341-4D24-9D1C-43002A45EDA8}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="7.109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="78.33203125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="59.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="13.77734375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.109375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="7.140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="86.5703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="64.42578125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="6.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
@@ -1245,7 +1173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30.75">
       <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
@@ -1255,12 +1183,10 @@
       <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="42" t="s">
-        <v>73</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="30.75">
       <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
@@ -1270,12 +1196,10 @@
       <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>74</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="30.75">
       <c r="A4" s="9" t="s">
         <v>23</v>
       </c>
@@ -1285,12 +1209,10 @@
       <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="43" t="s">
-        <v>75</v>
-      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30.75">
       <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
@@ -1300,12 +1222,10 @@
       <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="44" t="s">
-        <v>79</v>
-      </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="30.75">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
@@ -1315,12 +1235,10 @@
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="45" t="s">
-        <v>78</v>
-      </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="30.75">
       <c r="A7" s="9" t="s">
         <v>32</v>
       </c>
@@ -1330,12 +1248,10 @@
       <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="46" t="s">
-        <v>80</v>
-      </c>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="30.75">
       <c r="A8" s="9" t="s">
         <v>35</v>
       </c>
@@ -1345,12 +1261,10 @@
       <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="47" t="s">
-        <v>81</v>
-      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="30.75">
       <c r="A9" s="9" t="s">
         <v>36</v>
       </c>
@@ -1360,9 +1274,7 @@
       <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="48" t="s">
-        <v>82</v>
-      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
   </sheetData>
@@ -1373,17 +1285,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C97ADAC7-7831-4122-ACC2-6B9A4F5EE843}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="8" width="7.109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="8" width="84.6640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="8" width="64.44140625"/>
-    <col min="4" max="4" customWidth="true" style="16" width="14.77734375"/>
-    <col min="5" max="5" customWidth="true" style="8" width="37.44140625"/>
-    <col min="6" max="16384" style="8" width="9.109375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="8" width="7.140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="8" width="85.5703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="8" width="64.42578125"/>
+    <col min="4" max="4" customWidth="true" style="8" width="8.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="8" width="10.7109375"/>
+    <col min="6" max="16384" style="8" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
@@ -1400,7 +1312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30.75">
       <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
@@ -1410,51 +1322,49 @@
       <c r="C2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="49" t="s">
-        <v>73</v>
-      </c>
+      <c r="D2" s="9"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="60.75">
       <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="12" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="9"/>
       <c r="E3" s="9"/>
     </row>
-    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="60.75">
       <c r="A4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="9"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="60.75">
       <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="12" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="9"/>
     </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="30.75">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
@@ -1464,51 +1374,49 @@
       <c r="C6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="50" t="s">
-        <v>78</v>
-      </c>
+      <c r="D6" s="9"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="60.75">
       <c r="A7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="15"/>
+      <c r="D7" s="9"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="60.75">
       <c r="A8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>58</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="15"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="60.75">
       <c r="A9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="15"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="30.75">
       <c r="A10" s="9" t="s">
         <v>60</v>
       </c>
@@ -1518,12 +1426,10 @@
       <c r="C10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="51" t="s">
-        <v>83</v>
-      </c>
+      <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="30.75">
       <c r="A11" s="9" t="s">
         <v>63</v>
       </c>
@@ -1533,12 +1439,10 @@
       <c r="C11" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="52" t="s">
-        <v>84</v>
-      </c>
+      <c r="D11" s="9"/>
       <c r="E11" s="9"/>
     </row>
-    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="30.75">
       <c r="A12" s="9" t="s">
         <v>65</v>
       </c>
@@ -1548,12 +1452,10 @@
       <c r="C12" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="53" t="s">
-        <v>86</v>
-      </c>
+      <c r="D12" s="9"/>
       <c r="E12" s="9"/>
     </row>
-    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="30.75">
       <c r="A13" s="9" t="s">
         <v>67</v>
       </c>
@@ -1563,12 +1465,10 @@
       <c r="C13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="54" t="s">
-        <v>85</v>
-      </c>
+      <c r="D13" s="9"/>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="30.75">
       <c r="A14" s="9" t="s">
         <v>69</v>
       </c>
@@ -1578,12 +1478,10 @@
       <c r="C14" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="55" t="s">
-        <v>87</v>
-      </c>
+      <c r="D14" s="9"/>
       <c r="E14" s="9"/>
     </row>
-    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="30.75">
       <c r="A15" s="9" t="s">
         <v>71</v>
       </c>
@@ -1593,10 +1491,400 @@
       <c r="C15" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="56" t="s">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4965C2-E200-496B-8B4C-75F1F09D6C90}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="8" width="9.140625"/>
+    <col min="2" max="2" customWidth="true" style="8" width="79.7109375"/>
+    <col min="3" max="3" customWidth="true" style="8" width="83.0"/>
+    <col min="4" max="4" style="8" width="9.140625"/>
+    <col min="5" max="5" customWidth="true" style="8" width="21.5703125"/>
+    <col min="6" max="16384" style="8" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:5" ht="30.75">
+      <c r="A4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" ht="30.75">
+      <c r="A5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6" spans="1:5" ht="30.75">
+      <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" ht="30.75">
+      <c r="A7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{778900B1-9794-4101-8C74-6D9511BB5519}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="8" width="9.140625"/>
+    <col min="2" max="3" customWidth="true" style="8" width="80.85546875"/>
+    <col min="4" max="4" style="8" width="9.140625"/>
+    <col min="5" max="5" customWidth="true" style="8" width="22.0"/>
+    <col min="6" max="16384" style="8" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" ht="30.75">
+      <c r="A5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6" spans="1:5" ht="30.75">
+      <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" ht="30.75">
+      <c r="A7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+    </row>
+    <row r="8" spans="1:5" ht="30.75">
+      <c r="A8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:5" ht="30.75">
+      <c r="A9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:5" ht="30.75">
+      <c r="A10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:5" ht="30.75">
+      <c r="A11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+    </row>
+    <row r="12" spans="1:5" ht="30.75">
+      <c r="A12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A7BF9D-3833-414C-A234-5928A10163FB}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="3" customWidth="true" width="78.7109375"/>
+    <col min="5" max="5" customWidth="true" width="28.28515625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RST_SniperAI_Features_Automation/src/test/resources/TestDocuments/SAI_Login_Funtionality.xlsx
+++ b/RST_SniperAI_Features_Automation/src/test/resources/TestDocuments/SAI_Login_Funtionality.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="108">
   <si>
     <t>Sr No</t>
   </si>
@@ -318,6 +318,51 @@
   </si>
   <si>
     <t>TC_001: Passed</t>
+  </si>
+  <si>
+    <t>TC_002: SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_003: SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_004: SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_005: SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_006: SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_001: SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_007: SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_008: SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_002: Passed</t>
+  </si>
+  <si>
+    <t>TC_003: Passed</t>
+  </si>
+  <si>
+    <t>TC_004: Passed</t>
+  </si>
+  <si>
+    <t>TC_005: Passed</t>
+  </si>
+  <si>
+    <t>TC_006: Passed</t>
+  </si>
+  <si>
+    <t>TC_007: Passed</t>
+  </si>
+  <si>
+    <t>TC_008: Passed</t>
   </si>
 </sst>
 </file>
@@ -350,7 +395,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,6 +416,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -426,7 +481,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -464,6 +519,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1045,7 +1124,9 @@
       <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="30" t="s">
+        <v>92</v>
+      </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" ht="30.75">
@@ -1058,7 +1139,9 @@
       <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="31" t="s">
+        <v>101</v>
+      </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" ht="30.75">
@@ -1071,7 +1154,9 @@
       <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="33" t="s">
+        <v>102</v>
+      </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="30.75">
@@ -1084,7 +1169,9 @@
       <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="32" t="s">
+        <v>103</v>
+      </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="30.75">
@@ -1097,7 +1184,9 @@
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="34" t="s">
+        <v>104</v>
+      </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" ht="30.75">
@@ -1110,7 +1199,9 @@
       <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="35" t="s">
+        <v>105</v>
+      </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" ht="30.75">
@@ -1123,7 +1214,9 @@
       <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="36" t="s">
+        <v>106</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" ht="30.75">
@@ -1136,7 +1229,9 @@
       <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="37" t="s">
+        <v>107</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
   </sheetData>

--- a/RST_SniperAI_Features_Automation/src/test/resources/TestDocuments/SAI_Login_Funtionality.xlsx
+++ b/RST_SniperAI_Features_Automation/src/test/resources/TestDocuments/SAI_Login_Funtionality.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="108">
   <si>
     <t>Sr No</t>
   </si>
@@ -481,7 +481,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -536,6 +536,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
@@ -1124,7 +1140,7 @@
       <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="49" t="s">
         <v>92</v>
       </c>
       <c r="E2" s="2"/>
@@ -1139,7 +1155,7 @@
       <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="48" t="s">
         <v>101</v>
       </c>
       <c r="E3" s="2"/>
@@ -1154,7 +1170,7 @@
       <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="47" t="s">
         <v>102</v>
       </c>
       <c r="E4" s="2"/>
@@ -1169,7 +1185,7 @@
       <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="46" t="s">
         <v>103</v>
       </c>
       <c r="E5" s="2"/>
@@ -1184,7 +1200,7 @@
       <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="50" t="s">
         <v>104</v>
       </c>
       <c r="E6" s="2"/>
@@ -1199,7 +1215,7 @@
       <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="53" t="s">
         <v>105</v>
       </c>
       <c r="E7" s="2"/>
@@ -1214,7 +1230,7 @@
       <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="52" t="s">
         <v>106</v>
       </c>
       <c r="E8" s="2"/>
@@ -1229,7 +1245,7 @@
       <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="51" t="s">
         <v>107</v>
       </c>
       <c r="E9" s="2"/>
